--- a/data/Oficina_de_procuradora_de_mujeres/opmServiciosMes.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmServiciosMes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16820880-A808-40E2-8D01-F286862BBE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC73137-4BEC-4AC8-91AB-7CC7DF1BAA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7440" yWindow="1560" windowWidth="17280" windowHeight="9420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="5">
   <si>
     <t>Año</t>
   </si>
@@ -370,7 +370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -456,134 +456,167 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>2455</v>
+        <v>917</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
       </c>
       <c r="C9">
-        <v>2887</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
       </c>
       <c r="C10">
-        <v>2227</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
       </c>
       <c r="C11">
-        <v>2291</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
       </c>
       <c r="C12">
-        <v>2362</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
       </c>
       <c r="C13">
-        <v>2309</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="B14" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C14">
-        <v>3901</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="B15" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C15">
-        <v>5269</v>
+        <v>433</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>4909</v>
+        <v>3901</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
       </c>
       <c r="C17">
-        <v>3500</v>
+        <v>5269</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
       </c>
       <c r="C18">
-        <v>4413</v>
+        <v>4909</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>2024</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>4413</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>2025</v>
       </c>
-      <c r="B19" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19">
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21">
         <v>4173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>2026</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>499</v>
       </c>
     </row>
   </sheetData>
